--- a/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="574">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>
@@ -1236,6 +1236,21 @@
   </si>
   <si>
     <t xml:space="preserve">トウガラシ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bone mound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">骨塚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜骨</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 11.1</t>
@@ -1827,10 +1842,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C3" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1846,10 +1861,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C4" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1865,10 +1880,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C5" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -1884,10 +1899,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -1903,10 +1918,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C7" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1922,10 +1937,10 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C8" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -1941,10 +1956,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C9" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -1960,10 +1975,10 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C10" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -1979,10 +1994,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -1998,10 +2013,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C12" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -2017,10 +2032,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C13" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2036,10 +2051,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C14" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2055,10 +2070,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C15" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2074,10 +2089,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C16" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2093,10 +2108,10 @@
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C17" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D17" t="s">
         <v>50</v>
@@ -2112,10 +2127,10 @@
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C18" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D18" t="s">
         <v>44</v>
@@ -2131,10 +2146,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C19" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D19" t="s">
         <v>55</v>
@@ -2150,10 +2165,10 @@
         <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C20" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D20" t="s">
         <v>58</v>
@@ -2169,10 +2184,10 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C21" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D21" t="s">
         <v>61</v>
@@ -2188,10 +2203,10 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C22" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D22" t="s">
         <v>64</v>
@@ -2207,10 +2222,10 @@
         <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C23" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D23" t="s">
         <v>67</v>
@@ -2226,10 +2241,10 @@
         <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C24" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="D24" t="s">
         <v>70</v>
@@ -2245,10 +2260,10 @@
         <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C25" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D25" t="s">
         <v>73</v>
@@ -2264,10 +2279,10 @@
         <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C26" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D26" t="s">
         <v>76</v>
@@ -2283,10 +2298,10 @@
         <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C27" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
@@ -2302,10 +2317,10 @@
         <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C28" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D28" t="s">
         <v>82</v>
@@ -2321,10 +2336,10 @@
         <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C29" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D29" t="s">
         <v>85</v>
@@ -2340,10 +2355,10 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C30" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D30" t="s">
         <v>88</v>
@@ -2359,10 +2374,10 @@
         <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C31" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D31" t="s">
         <v>91</v>
@@ -2378,10 +2393,10 @@
         <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C32" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D32" t="s">
         <v>94</v>
@@ -2397,10 +2412,10 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C33" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D33" t="s">
         <v>97</v>
@@ -2416,10 +2431,10 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C34" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D34" t="s">
         <v>100</v>
@@ -2435,10 +2450,10 @@
         <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C35" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D35" t="s">
         <v>103</v>
@@ -2454,10 +2469,10 @@
         <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C36" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D36" t="s">
         <v>106</v>
@@ -2473,10 +2488,10 @@
         <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C37" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -2492,10 +2507,10 @@
         <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C38" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D38" t="s">
         <v>112</v>
@@ -2511,10 +2526,10 @@
         <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C39" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D39" t="s">
         <v>115</v>
@@ -2530,10 +2545,10 @@
         <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C40" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D40" t="s">
         <v>118</v>
@@ -2549,10 +2564,10 @@
         <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C41" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D41" t="s">
         <v>121</v>
@@ -2568,10 +2583,10 @@
         <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C42" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D42" t="s">
         <v>124</v>
@@ -2587,10 +2602,10 @@
         <v>126</v>
       </c>
       <c r="B43" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C43" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D43" t="s">
         <v>127</v>
@@ -2606,10 +2621,10 @@
         <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C44" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D44" t="s">
         <v>130</v>
@@ -2625,10 +2640,10 @@
         <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C45" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D45" t="s">
         <v>133</v>
@@ -2644,10 +2659,10 @@
         <v>135</v>
       </c>
       <c r="B46" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C46" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D46" t="s">
         <v>82</v>
@@ -2663,10 +2678,10 @@
         <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C47" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D47" t="s">
         <v>138</v>
@@ -2682,10 +2697,10 @@
         <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C48" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D48" t="s">
         <v>141</v>
@@ -2701,10 +2716,10 @@
         <v>143</v>
       </c>
       <c r="B49" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C49" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -2720,10 +2735,10 @@
         <v>144</v>
       </c>
       <c r="B50" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C50" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D50" t="s">
         <v>44</v>
@@ -2739,10 +2754,10 @@
         <v>146</v>
       </c>
       <c r="B51" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C51" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D51" t="s">
         <v>147</v>
@@ -2758,10 +2773,10 @@
         <v>149</v>
       </c>
       <c r="B52" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C52" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D52" t="s">
         <v>150</v>
@@ -2777,10 +2792,10 @@
         <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C53" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D53" t="s">
         <v>153</v>
@@ -2796,10 +2811,10 @@
         <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C54" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D54" t="s">
         <v>156</v>
@@ -2815,10 +2830,10 @@
         <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C55" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D55" t="s">
         <v>159</v>
@@ -2834,10 +2849,10 @@
         <v>161</v>
       </c>
       <c r="B56" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C56" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D56" t="s">
         <v>162</v>
@@ -2853,10 +2868,10 @@
         <v>164</v>
       </c>
       <c r="B57" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C57" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D57" t="s">
         <v>165</v>
@@ -2872,10 +2887,10 @@
         <v>167</v>
       </c>
       <c r="B58" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C58" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D58" t="s">
         <v>168</v>
@@ -2891,10 +2906,10 @@
         <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C59" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="D59" t="s">
         <v>171</v>
@@ -2910,10 +2925,10 @@
         <v>173</v>
       </c>
       <c r="B60" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C60" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D60" t="s">
         <v>174</v>
@@ -2929,10 +2944,10 @@
         <v>176</v>
       </c>
       <c r="B61" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C61" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D61" t="s">
         <v>177</v>
@@ -2948,10 +2963,10 @@
         <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C62" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D62" t="s">
         <v>180</v>
@@ -2967,10 +2982,10 @@
         <v>182</v>
       </c>
       <c r="B63" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C63" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D63" t="s">
         <v>183</v>
@@ -2986,10 +3001,10 @@
         <v>185</v>
       </c>
       <c r="B64" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C64" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D64" t="s">
         <v>186</v>
@@ -3005,10 +3020,10 @@
         <v>188</v>
       </c>
       <c r="B65" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C65" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D65" t="s">
         <v>189</v>
@@ -3024,10 +3039,10 @@
         <v>191</v>
       </c>
       <c r="B66" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C66" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D66" t="s">
         <v>192</v>
@@ -3043,10 +3058,10 @@
         <v>194</v>
       </c>
       <c r="B67" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C67" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D67" t="s">
         <v>195</v>
@@ -3062,10 +3077,10 @@
         <v>197</v>
       </c>
       <c r="B68" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C68" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="D68" t="s">
         <v>198</v>
@@ -3081,10 +3096,10 @@
         <v>200</v>
       </c>
       <c r="B69" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C69" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D69" t="s">
         <v>201</v>
@@ -3100,10 +3115,10 @@
         <v>203</v>
       </c>
       <c r="B70" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C70" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D70" t="s">
         <v>204</v>
@@ -3119,10 +3134,10 @@
         <v>206</v>
       </c>
       <c r="B71" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C71" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D71" t="s">
         <v>207</v>
@@ -3138,10 +3153,10 @@
         <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C72" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D72" t="s">
         <v>210</v>
@@ -3157,10 +3172,10 @@
         <v>212</v>
       </c>
       <c r="B73" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C73" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D73" t="s">
         <v>213</v>
@@ -3176,10 +3191,10 @@
         <v>215</v>
       </c>
       <c r="B74" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C74" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D74" t="s">
         <v>216</v>
@@ -3195,10 +3210,10 @@
         <v>218</v>
       </c>
       <c r="B75" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C75" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D75" t="s">
         <v>219</v>
@@ -3214,10 +3229,10 @@
         <v>221</v>
       </c>
       <c r="B76" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C76" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D76" t="s">
         <v>222</v>
@@ -3233,10 +3248,10 @@
         <v>224</v>
       </c>
       <c r="B77" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C77" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D77" t="s">
         <v>225</v>
@@ -3252,10 +3267,10 @@
         <v>227</v>
       </c>
       <c r="B78" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C78" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D78" t="s">
         <v>228</v>
@@ -3271,10 +3286,10 @@
         <v>230</v>
       </c>
       <c r="B79" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C79" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="D79" t="s">
         <v>231</v>
@@ -3290,10 +3305,10 @@
         <v>233</v>
       </c>
       <c r="B80" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C80" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D80" t="s">
         <v>234</v>
@@ -3309,10 +3324,10 @@
         <v>236</v>
       </c>
       <c r="B81" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C81" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="D81" t="s">
         <v>237</v>
@@ -3328,10 +3343,10 @@
         <v>239</v>
       </c>
       <c r="B82" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C82" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="D82" t="s">
         <v>240</v>
@@ -3347,10 +3362,10 @@
         <v>242</v>
       </c>
       <c r="B83" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C83" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D83" t="s">
         <v>243</v>
@@ -3366,10 +3381,10 @@
         <v>244</v>
       </c>
       <c r="B84" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C84" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="D84" t="s">
         <v>245</v>
@@ -3385,10 +3400,10 @@
         <v>247</v>
       </c>
       <c r="B85" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C85" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D85" t="s">
         <v>248</v>
@@ -3404,10 +3419,10 @@
         <v>250</v>
       </c>
       <c r="B86" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C86" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D86" t="s">
         <v>109</v>
@@ -3423,10 +3438,10 @@
         <v>251</v>
       </c>
       <c r="B87" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C87" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D87" t="s">
         <v>252</v>
@@ -3442,10 +3457,10 @@
         <v>254</v>
       </c>
       <c r="B88" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C88" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D88" t="s">
         <v>109</v>
@@ -3461,10 +3476,10 @@
         <v>255</v>
       </c>
       <c r="B89" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C89" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D89" t="s">
         <v>109</v>
@@ -3480,10 +3495,10 @@
         <v>256</v>
       </c>
       <c r="B90" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C90" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D90" t="s">
         <v>109</v>
@@ -3499,10 +3514,10 @@
         <v>257</v>
       </c>
       <c r="B91" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C91" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D91" t="s">
         <v>258</v>
@@ -3518,10 +3533,10 @@
         <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C92" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D92" t="s">
         <v>261</v>
@@ -3537,10 +3552,10 @@
         <v>263</v>
       </c>
       <c r="B93" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C93" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D93" t="s">
         <v>264</v>
@@ -3556,10 +3571,10 @@
         <v>266</v>
       </c>
       <c r="B94" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C94" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="D94" t="s">
         <v>267</v>
@@ -3575,10 +3590,10 @@
         <v>269</v>
       </c>
       <c r="B95" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C95" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D95" t="s">
         <v>270</v>
@@ -3594,10 +3609,10 @@
         <v>272</v>
       </c>
       <c r="B96" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C96" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="D96" t="s">
         <v>273</v>
@@ -3613,10 +3628,10 @@
         <v>275</v>
       </c>
       <c r="B97" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C97" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D97" t="s">
         <v>276</v>
@@ -3632,10 +3647,10 @@
         <v>278</v>
       </c>
       <c r="B98" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C98" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="D98" t="s">
         <v>279</v>
@@ -3651,10 +3666,10 @@
         <v>281</v>
       </c>
       <c r="B99" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C99" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="D99" t="s">
         <v>279</v>
@@ -3670,10 +3685,10 @@
         <v>282</v>
       </c>
       <c r="B100" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C100" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D100" t="s">
         <v>100</v>
@@ -3689,10 +3704,10 @@
         <v>283</v>
       </c>
       <c r="B101" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C101" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D101" t="s">
         <v>100</v>
@@ -3708,10 +3723,10 @@
         <v>284</v>
       </c>
       <c r="B102" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C102" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D102" t="s">
         <v>285</v>
@@ -3727,10 +3742,10 @@
         <v>287</v>
       </c>
       <c r="B103" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C103" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="D103" t="s">
         <v>288</v>
@@ -3746,10 +3761,10 @@
         <v>290</v>
       </c>
       <c r="B104" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C104" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="D104" t="s">
         <v>79</v>
@@ -3765,10 +3780,10 @@
         <v>291</v>
       </c>
       <c r="B105" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C105" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="D105" t="s">
         <v>292</v>
@@ -3784,10 +3799,10 @@
         <v>294</v>
       </c>
       <c r="B106" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C106" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="D106" t="s">
         <v>295</v>
@@ -3803,10 +3818,10 @@
         <v>297</v>
       </c>
       <c r="B107" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C107" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D107" t="s">
         <v>298</v>
@@ -3822,10 +3837,10 @@
         <v>300</v>
       </c>
       <c r="B108" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C108" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D108" t="s">
         <v>301</v>
@@ -3841,10 +3856,10 @@
         <v>303</v>
       </c>
       <c r="B109" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C109" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="D109" t="s">
         <v>79</v>
@@ -3860,10 +3875,10 @@
         <v>304</v>
       </c>
       <c r="B110" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C110" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="D110" t="s">
         <v>305</v>
@@ -3879,10 +3894,10 @@
         <v>307</v>
       </c>
       <c r="B111" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C111" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D111" t="s">
         <v>308</v>
@@ -3898,10 +3913,10 @@
         <v>310</v>
       </c>
       <c r="B112" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C112" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="D112" t="s">
         <v>311</v>
@@ -3917,10 +3932,10 @@
         <v>313</v>
       </c>
       <c r="B113" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C113" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D113" t="s">
         <v>314</v>
@@ -3936,10 +3951,10 @@
         <v>316</v>
       </c>
       <c r="B114" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C114" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="D114" t="s">
         <v>317</v>
@@ -3955,10 +3970,10 @@
         <v>319</v>
       </c>
       <c r="B115" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C115" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D115" t="s">
         <v>320</v>
@@ -3974,10 +3989,10 @@
         <v>322</v>
       </c>
       <c r="B116" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C116" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D116" t="s">
         <v>323</v>
@@ -3993,10 +4008,10 @@
         <v>325</v>
       </c>
       <c r="B117" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C117" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D117" t="s">
         <v>326</v>
@@ -4012,10 +4027,10 @@
         <v>328</v>
       </c>
       <c r="B118" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C118" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D118" t="s">
         <v>329</v>
@@ -4031,10 +4046,10 @@
         <v>331</v>
       </c>
       <c r="B119" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C119" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="D119" t="s">
         <v>332</v>
@@ -4050,10 +4065,10 @@
         <v>334</v>
       </c>
       <c r="B120" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C120" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D120" t="s">
         <v>335</v>
@@ -4069,10 +4084,10 @@
         <v>337</v>
       </c>
       <c r="B121" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C121" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D121" t="s">
         <v>338</v>
@@ -4088,10 +4103,10 @@
         <v>340</v>
       </c>
       <c r="B122" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C122" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D122" t="s">
         <v>341</v>
@@ -4107,10 +4122,10 @@
         <v>343</v>
       </c>
       <c r="B123" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C123" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D123" t="s">
         <v>22</v>
@@ -4126,10 +4141,10 @@
         <v>344</v>
       </c>
       <c r="B124" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C124" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D124" t="s">
         <v>345</v>
@@ -4145,10 +4160,10 @@
         <v>347</v>
       </c>
       <c r="B125" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C125" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D125" t="s">
         <v>348</v>
@@ -4164,10 +4179,10 @@
         <v>350</v>
       </c>
       <c r="B126" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C126" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D126" t="s">
         <v>351</v>
@@ -4183,10 +4198,10 @@
         <v>353</v>
       </c>
       <c r="B127" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C127" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D127" t="s">
         <v>354</v>
@@ -4202,10 +4217,10 @@
         <v>356</v>
       </c>
       <c r="B128" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C128" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D128" t="s">
         <v>357</v>
@@ -4221,10 +4236,10 @@
         <v>359</v>
       </c>
       <c r="B129" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C129" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D129" t="s">
         <v>360</v>
@@ -4240,10 +4255,10 @@
         <v>362</v>
       </c>
       <c r="B130" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C130" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D130" t="s">
         <v>363</v>
@@ -4259,10 +4274,10 @@
         <v>365</v>
       </c>
       <c r="B131" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C131" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="D131" t="s">
         <v>366</v>
@@ -4278,10 +4293,10 @@
         <v>368</v>
       </c>
       <c r="B132" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C132" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D132" t="s">
         <v>369</v>
@@ -4297,10 +4312,10 @@
         <v>371</v>
       </c>
       <c r="B133" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C133" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D133" t="s">
         <v>372</v>
@@ -4316,10 +4331,10 @@
         <v>374</v>
       </c>
       <c r="B134" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C134" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D134" t="s">
         <v>375</v>
@@ -4335,10 +4350,10 @@
         <v>377</v>
       </c>
       <c r="B135" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C135" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="D135" t="s">
         <v>378</v>
@@ -4354,10 +4369,10 @@
         <v>380</v>
       </c>
       <c r="B136" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C136" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="D136" t="s">
         <v>381</v>
@@ -4373,10 +4388,10 @@
         <v>383</v>
       </c>
       <c r="B137" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C137" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="D137" t="s">
         <v>384</v>
@@ -4392,10 +4407,10 @@
         <v>386</v>
       </c>
       <c r="B138" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C138" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D138" t="s">
         <v>387</v>
@@ -4411,10 +4426,10 @@
         <v>389</v>
       </c>
       <c r="B139" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C139" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D139" t="s">
         <v>390</v>
@@ -4430,10 +4445,10 @@
         <v>392</v>
       </c>
       <c r="B140" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C140" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D140" t="s">
         <v>393</v>
@@ -4449,10 +4464,10 @@
         <v>395</v>
       </c>
       <c r="B141" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C141" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D141" t="s">
         <v>396</v>
@@ -4468,10 +4483,10 @@
         <v>398</v>
       </c>
       <c r="B142" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C142" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D142" t="s">
         <v>399</v>
@@ -4487,10 +4502,10 @@
         <v>401</v>
       </c>
       <c r="B143" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C143" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D143" t="s">
         <v>402</v>
@@ -4506,10 +4521,10 @@
         <v>404</v>
       </c>
       <c r="B144" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C144" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D144" t="s">
         <v>405</v>
@@ -4519,6 +4534,38 @@
       </c>
       <c r="G144"/>
       <c r="H144"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>407</v>
+      </c>
+      <c r="B145" t="s">
+        <v>9</v>
+      </c>
+      <c r="D145" t="s">
+        <v>408</v>
+      </c>
+      <c r="E145" t="s">
+        <v>409</v>
+      </c>
+      <c r="G145"/>
+      <c r="H145"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>410</v>
+      </c>
+      <c r="B146" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146" t="s">
+        <v>159</v>
+      </c>
+      <c r="E146" t="s">
+        <v>411</v>
+      </c>
+      <c r="G146"/>
+      <c r="H146"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="580">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>
@@ -1251,6 +1251,15 @@
   </si>
   <si>
     <t xml:space="preserve">竜骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stepping stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">踏み石</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 11.1</t>
@@ -1851,10 +1860,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1870,10 +1879,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C4" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1889,10 +1898,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C5" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -1908,10 +1917,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C6" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -1927,10 +1936,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C7" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1946,10 +1955,10 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -1965,10 +1974,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C9" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -1984,10 +1993,10 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -2003,10 +2012,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C11" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2022,10 +2031,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C12" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -2041,10 +2050,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2060,10 +2069,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C14" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2079,10 +2088,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2098,10 +2107,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C16" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2117,10 +2126,10 @@
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C17" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D17" t="s">
         <v>50</v>
@@ -2136,10 +2145,10 @@
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C18" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D18" t="s">
         <v>44</v>
@@ -2155,10 +2164,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C19" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D19" t="s">
         <v>55</v>
@@ -2174,10 +2183,10 @@
         <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C20" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D20" t="s">
         <v>58</v>
@@ -2193,10 +2202,10 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C21" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D21" t="s">
         <v>61</v>
@@ -2212,10 +2221,10 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C22" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D22" t="s">
         <v>64</v>
@@ -2231,10 +2240,10 @@
         <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C23" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D23" t="s">
         <v>67</v>
@@ -2250,10 +2259,10 @@
         <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C24" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D24" t="s">
         <v>70</v>
@@ -2269,10 +2278,10 @@
         <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C25" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D25" t="s">
         <v>73</v>
@@ -2288,10 +2297,10 @@
         <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C26" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D26" t="s">
         <v>76</v>
@@ -2307,10 +2316,10 @@
         <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C27" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
@@ -2326,10 +2335,10 @@
         <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C28" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D28" t="s">
         <v>82</v>
@@ -2345,10 +2354,10 @@
         <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C29" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D29" t="s">
         <v>85</v>
@@ -2364,10 +2373,10 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C30" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D30" t="s">
         <v>88</v>
@@ -2383,10 +2392,10 @@
         <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C31" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D31" t="s">
         <v>91</v>
@@ -2402,10 +2411,10 @@
         <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C32" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D32" t="s">
         <v>94</v>
@@ -2421,10 +2430,10 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C33" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D33" t="s">
         <v>97</v>
@@ -2440,10 +2449,10 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C34" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D34" t="s">
         <v>100</v>
@@ -2459,10 +2468,10 @@
         <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C35" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D35" t="s">
         <v>103</v>
@@ -2478,10 +2487,10 @@
         <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C36" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D36" t="s">
         <v>106</v>
@@ -2497,10 +2506,10 @@
         <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C37" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -2516,10 +2525,10 @@
         <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C38" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D38" t="s">
         <v>112</v>
@@ -2535,10 +2544,10 @@
         <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C39" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D39" t="s">
         <v>115</v>
@@ -2554,10 +2563,10 @@
         <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C40" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D40" t="s">
         <v>118</v>
@@ -2573,10 +2582,10 @@
         <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C41" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D41" t="s">
         <v>121</v>
@@ -2592,10 +2601,10 @@
         <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C42" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D42" t="s">
         <v>124</v>
@@ -2611,10 +2620,10 @@
         <v>126</v>
       </c>
       <c r="B43" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C43" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D43" t="s">
         <v>127</v>
@@ -2630,10 +2639,10 @@
         <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C44" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D44" t="s">
         <v>130</v>
@@ -2649,10 +2658,10 @@
         <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C45" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D45" t="s">
         <v>133</v>
@@ -2668,10 +2677,10 @@
         <v>135</v>
       </c>
       <c r="B46" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C46" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D46" t="s">
         <v>82</v>
@@ -2687,10 +2696,10 @@
         <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C47" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D47" t="s">
         <v>138</v>
@@ -2706,10 +2715,10 @@
         <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C48" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D48" t="s">
         <v>141</v>
@@ -2725,10 +2734,10 @@
         <v>143</v>
       </c>
       <c r="B49" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C49" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -2744,10 +2753,10 @@
         <v>144</v>
       </c>
       <c r="B50" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C50" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D50" t="s">
         <v>44</v>
@@ -2763,10 +2772,10 @@
         <v>146</v>
       </c>
       <c r="B51" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C51" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D51" t="s">
         <v>147</v>
@@ -2782,10 +2791,10 @@
         <v>149</v>
       </c>
       <c r="B52" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C52" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D52" t="s">
         <v>150</v>
@@ -2801,10 +2810,10 @@
         <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C53" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D53" t="s">
         <v>153</v>
@@ -2820,10 +2829,10 @@
         <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C54" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D54" t="s">
         <v>156</v>
@@ -2839,10 +2848,10 @@
         <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C55" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D55" t="s">
         <v>159</v>
@@ -2858,10 +2867,10 @@
         <v>161</v>
       </c>
       <c r="B56" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C56" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D56" t="s">
         <v>162</v>
@@ -2877,10 +2886,10 @@
         <v>164</v>
       </c>
       <c r="B57" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C57" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D57" t="s">
         <v>165</v>
@@ -2896,10 +2905,10 @@
         <v>167</v>
       </c>
       <c r="B58" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C58" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D58" t="s">
         <v>168</v>
@@ -2915,10 +2924,10 @@
         <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C59" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D59" t="s">
         <v>171</v>
@@ -2934,10 +2943,10 @@
         <v>173</v>
       </c>
       <c r="B60" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C60" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D60" t="s">
         <v>174</v>
@@ -2953,10 +2962,10 @@
         <v>176</v>
       </c>
       <c r="B61" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C61" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D61" t="s">
         <v>177</v>
@@ -2972,10 +2981,10 @@
         <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C62" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D62" t="s">
         <v>180</v>
@@ -2991,10 +3000,10 @@
         <v>182</v>
       </c>
       <c r="B63" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C63" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D63" t="s">
         <v>183</v>
@@ -3010,10 +3019,10 @@
         <v>185</v>
       </c>
       <c r="B64" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C64" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D64" t="s">
         <v>186</v>
@@ -3029,10 +3038,10 @@
         <v>188</v>
       </c>
       <c r="B65" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C65" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D65" t="s">
         <v>189</v>
@@ -3048,10 +3057,10 @@
         <v>191</v>
       </c>
       <c r="B66" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C66" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D66" t="s">
         <v>192</v>
@@ -3067,10 +3076,10 @@
         <v>194</v>
       </c>
       <c r="B67" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C67" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D67" t="s">
         <v>195</v>
@@ -3086,10 +3095,10 @@
         <v>197</v>
       </c>
       <c r="B68" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C68" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D68" t="s">
         <v>198</v>
@@ -3105,10 +3114,10 @@
         <v>200</v>
       </c>
       <c r="B69" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C69" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D69" t="s">
         <v>201</v>
@@ -3124,10 +3133,10 @@
         <v>203</v>
       </c>
       <c r="B70" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C70" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D70" t="s">
         <v>204</v>
@@ -3143,10 +3152,10 @@
         <v>206</v>
       </c>
       <c r="B71" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C71" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D71" t="s">
         <v>207</v>
@@ -3162,10 +3171,10 @@
         <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C72" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D72" t="s">
         <v>210</v>
@@ -3181,10 +3190,10 @@
         <v>212</v>
       </c>
       <c r="B73" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C73" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D73" t="s">
         <v>213</v>
@@ -3200,10 +3209,10 @@
         <v>215</v>
       </c>
       <c r="B74" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C74" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D74" t="s">
         <v>216</v>
@@ -3219,10 +3228,10 @@
         <v>218</v>
       </c>
       <c r="B75" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C75" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D75" t="s">
         <v>219</v>
@@ -3238,10 +3247,10 @@
         <v>221</v>
       </c>
       <c r="B76" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C76" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D76" t="s">
         <v>222</v>
@@ -3257,10 +3266,10 @@
         <v>224</v>
       </c>
       <c r="B77" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C77" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D77" t="s">
         <v>225</v>
@@ -3276,10 +3285,10 @@
         <v>227</v>
       </c>
       <c r="B78" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C78" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D78" t="s">
         <v>228</v>
@@ -3295,10 +3304,10 @@
         <v>230</v>
       </c>
       <c r="B79" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C79" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D79" t="s">
         <v>231</v>
@@ -3314,10 +3323,10 @@
         <v>233</v>
       </c>
       <c r="B80" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C80" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D80" t="s">
         <v>234</v>
@@ -3333,10 +3342,10 @@
         <v>236</v>
       </c>
       <c r="B81" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C81" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D81" t="s">
         <v>237</v>
@@ -3352,10 +3361,10 @@
         <v>239</v>
       </c>
       <c r="B82" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C82" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D82" t="s">
         <v>240</v>
@@ -3371,10 +3380,10 @@
         <v>242</v>
       </c>
       <c r="B83" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C83" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D83" t="s">
         <v>243</v>
@@ -3390,10 +3399,10 @@
         <v>244</v>
       </c>
       <c r="B84" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C84" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D84" t="s">
         <v>245</v>
@@ -3409,10 +3418,10 @@
         <v>247</v>
       </c>
       <c r="B85" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C85" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D85" t="s">
         <v>248</v>
@@ -3428,10 +3437,10 @@
         <v>250</v>
       </c>
       <c r="B86" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C86" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D86" t="s">
         <v>109</v>
@@ -3447,10 +3456,10 @@
         <v>251</v>
       </c>
       <c r="B87" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C87" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D87" t="s">
         <v>252</v>
@@ -3466,10 +3475,10 @@
         <v>254</v>
       </c>
       <c r="B88" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C88" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D88" t="s">
         <v>109</v>
@@ -3485,10 +3494,10 @@
         <v>255</v>
       </c>
       <c r="B89" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C89" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D89" t="s">
         <v>109</v>
@@ -3504,10 +3513,10 @@
         <v>256</v>
       </c>
       <c r="B90" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C90" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D90" t="s">
         <v>109</v>
@@ -3523,10 +3532,10 @@
         <v>257</v>
       </c>
       <c r="B91" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C91" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D91" t="s">
         <v>258</v>
@@ -3542,10 +3551,10 @@
         <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C92" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D92" t="s">
         <v>261</v>
@@ -3561,10 +3570,10 @@
         <v>263</v>
       </c>
       <c r="B93" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C93" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D93" t="s">
         <v>264</v>
@@ -3580,10 +3589,10 @@
         <v>266</v>
       </c>
       <c r="B94" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C94" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D94" t="s">
         <v>267</v>
@@ -3599,10 +3608,10 @@
         <v>269</v>
       </c>
       <c r="B95" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C95" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D95" t="s">
         <v>270</v>
@@ -3618,10 +3627,10 @@
         <v>272</v>
       </c>
       <c r="B96" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C96" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D96" t="s">
         <v>273</v>
@@ -3637,10 +3646,10 @@
         <v>275</v>
       </c>
       <c r="B97" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C97" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D97" t="s">
         <v>276</v>
@@ -3656,10 +3665,10 @@
         <v>278</v>
       </c>
       <c r="B98" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C98" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D98" t="s">
         <v>279</v>
@@ -3675,10 +3684,10 @@
         <v>281</v>
       </c>
       <c r="B99" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C99" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D99" t="s">
         <v>279</v>
@@ -3694,10 +3703,10 @@
         <v>282</v>
       </c>
       <c r="B100" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C100" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D100" t="s">
         <v>100</v>
@@ -3713,10 +3722,10 @@
         <v>283</v>
       </c>
       <c r="B101" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C101" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D101" t="s">
         <v>100</v>
@@ -3732,10 +3741,10 @@
         <v>284</v>
       </c>
       <c r="B102" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C102" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D102" t="s">
         <v>285</v>
@@ -3751,10 +3760,10 @@
         <v>287</v>
       </c>
       <c r="B103" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C103" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D103" t="s">
         <v>288</v>
@@ -3770,10 +3779,10 @@
         <v>290</v>
       </c>
       <c r="B104" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C104" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D104" t="s">
         <v>79</v>
@@ -3789,10 +3798,10 @@
         <v>291</v>
       </c>
       <c r="B105" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C105" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D105" t="s">
         <v>292</v>
@@ -3808,10 +3817,10 @@
         <v>294</v>
       </c>
       <c r="B106" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C106" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D106" t="s">
         <v>295</v>
@@ -3827,10 +3836,10 @@
         <v>297</v>
       </c>
       <c r="B107" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C107" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D107" t="s">
         <v>298</v>
@@ -3846,10 +3855,10 @@
         <v>300</v>
       </c>
       <c r="B108" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C108" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D108" t="s">
         <v>301</v>
@@ -3865,10 +3874,10 @@
         <v>303</v>
       </c>
       <c r="B109" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C109" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D109" t="s">
         <v>79</v>
@@ -3884,10 +3893,10 @@
         <v>304</v>
       </c>
       <c r="B110" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C110" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D110" t="s">
         <v>305</v>
@@ -3903,10 +3912,10 @@
         <v>307</v>
       </c>
       <c r="B111" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C111" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D111" t="s">
         <v>308</v>
@@ -3922,10 +3931,10 @@
         <v>310</v>
       </c>
       <c r="B112" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C112" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D112" t="s">
         <v>311</v>
@@ -3941,10 +3950,10 @@
         <v>313</v>
       </c>
       <c r="B113" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C113" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D113" t="s">
         <v>314</v>
@@ -3960,10 +3969,10 @@
         <v>316</v>
       </c>
       <c r="B114" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C114" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D114" t="s">
         <v>317</v>
@@ -3979,10 +3988,10 @@
         <v>319</v>
       </c>
       <c r="B115" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C115" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D115" t="s">
         <v>320</v>
@@ -3998,10 +4007,10 @@
         <v>322</v>
       </c>
       <c r="B116" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C116" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D116" t="s">
         <v>323</v>
@@ -4017,10 +4026,10 @@
         <v>325</v>
       </c>
       <c r="B117" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C117" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D117" t="s">
         <v>326</v>
@@ -4036,10 +4045,10 @@
         <v>328</v>
       </c>
       <c r="B118" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C118" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D118" t="s">
         <v>329</v>
@@ -4055,10 +4064,10 @@
         <v>331</v>
       </c>
       <c r="B119" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D119" t="s">
         <v>332</v>
@@ -4074,10 +4083,10 @@
         <v>334</v>
       </c>
       <c r="B120" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C120" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D120" t="s">
         <v>335</v>
@@ -4093,10 +4102,10 @@
         <v>337</v>
       </c>
       <c r="B121" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C121" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D121" t="s">
         <v>338</v>
@@ -4112,10 +4121,10 @@
         <v>340</v>
       </c>
       <c r="B122" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C122" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D122" t="s">
         <v>341</v>
@@ -4131,10 +4140,10 @@
         <v>343</v>
       </c>
       <c r="B123" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C123" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D123" t="s">
         <v>22</v>
@@ -4150,10 +4159,10 @@
         <v>344</v>
       </c>
       <c r="B124" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C124" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D124" t="s">
         <v>345</v>
@@ -4169,10 +4178,10 @@
         <v>347</v>
       </c>
       <c r="B125" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C125" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D125" t="s">
         <v>348</v>
@@ -4188,10 +4197,10 @@
         <v>350</v>
       </c>
       <c r="B126" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C126" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D126" t="s">
         <v>351</v>
@@ -4207,10 +4216,10 @@
         <v>353</v>
       </c>
       <c r="B127" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C127" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D127" t="s">
         <v>354</v>
@@ -4226,10 +4235,10 @@
         <v>356</v>
       </c>
       <c r="B128" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C128" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D128" t="s">
         <v>357</v>
@@ -4245,10 +4254,10 @@
         <v>359</v>
       </c>
       <c r="B129" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C129" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D129" t="s">
         <v>360</v>
@@ -4264,10 +4273,10 @@
         <v>362</v>
       </c>
       <c r="B130" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C130" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D130" t="s">
         <v>363</v>
@@ -4283,10 +4292,10 @@
         <v>365</v>
       </c>
       <c r="B131" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C131" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D131" t="s">
         <v>366</v>
@@ -4302,10 +4311,10 @@
         <v>368</v>
       </c>
       <c r="B132" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C132" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D132" t="s">
         <v>369</v>
@@ -4321,10 +4330,10 @@
         <v>371</v>
       </c>
       <c r="B133" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C133" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D133" t="s">
         <v>372</v>
@@ -4340,10 +4349,10 @@
         <v>374</v>
       </c>
       <c r="B134" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C134" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D134" t="s">
         <v>375</v>
@@ -4359,10 +4368,10 @@
         <v>377</v>
       </c>
       <c r="B135" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C135" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D135" t="s">
         <v>378</v>
@@ -4378,10 +4387,10 @@
         <v>380</v>
       </c>
       <c r="B136" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C136" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D136" t="s">
         <v>381</v>
@@ -4397,10 +4406,10 @@
         <v>383</v>
       </c>
       <c r="B137" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C137" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D137" t="s">
         <v>384</v>
@@ -4416,10 +4425,10 @@
         <v>386</v>
       </c>
       <c r="B138" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C138" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D138" t="s">
         <v>387</v>
@@ -4435,10 +4444,10 @@
         <v>389</v>
       </c>
       <c r="B139" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C139" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D139" t="s">
         <v>390</v>
@@ -4454,10 +4463,10 @@
         <v>392</v>
       </c>
       <c r="B140" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C140" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D140" t="s">
         <v>393</v>
@@ -4473,10 +4482,10 @@
         <v>395</v>
       </c>
       <c r="B141" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C141" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D141" t="s">
         <v>396</v>
@@ -4492,10 +4501,10 @@
         <v>398</v>
       </c>
       <c r="B142" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C142" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D142" t="s">
         <v>399</v>
@@ -4511,10 +4520,10 @@
         <v>401</v>
       </c>
       <c r="B143" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C143" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D143" t="s">
         <v>402</v>
@@ -4530,10 +4539,10 @@
         <v>404</v>
       </c>
       <c r="B144" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C144" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D144" t="s">
         <v>405</v>
@@ -4549,10 +4558,10 @@
         <v>407</v>
       </c>
       <c r="B145" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C145" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D145" t="s">
         <v>408</v>
@@ -4568,10 +4577,10 @@
         <v>410</v>
       </c>
       <c r="B146" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C146" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D146" t="s">
         <v>159</v>
@@ -4581,6 +4590,22 @@
       </c>
       <c r="G146"/>
       <c r="H146"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>412</v>
+      </c>
+      <c r="B147" t="s">
+        <v>9</v>
+      </c>
+      <c r="D147" t="s">
+        <v>413</v>
+      </c>
+      <c r="E147" t="s">
+        <v>414</v>
+      </c>
+      <c r="G147"/>
+      <c r="H147"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="587">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">24</t>
   </si>
   <si>
-    <t xml:space="preserve">wall frame</t>
+    <t xml:space="preserve">wooden frame</t>
   </si>
   <si>
     <t xml:space="preserve">木枠</t>
@@ -929,6 +929,12 @@
     <t xml:space="preserve">106</t>
   </si>
   <si>
+    <t xml:space="preserve">metal frame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄枠</t>
+  </si>
+  <si>
     <t xml:space="preserve">107</t>
   </si>
   <si>
@@ -1260,6 +1266,15 @@
   </si>
   <si>
     <t xml:space="preserve">踏み石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卵</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 11.1</t>
@@ -1866,10 +1881,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C3" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1885,10 +1900,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C4" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1904,10 +1919,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C5" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -1923,10 +1938,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C6" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -1942,10 +1957,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1961,10 +1976,10 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C8" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -1980,10 +1995,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C9" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -1999,10 +2014,10 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C10" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -2018,10 +2033,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2037,10 +2052,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C12" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -2056,10 +2071,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C13" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2075,10 +2090,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C14" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2094,10 +2109,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C15" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2113,10 +2128,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C16" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2132,10 +2147,10 @@
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C17" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D17" t="s">
         <v>50</v>
@@ -2151,10 +2166,10 @@
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C18" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D18" t="s">
         <v>44</v>
@@ -2170,10 +2185,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C19" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D19" t="s">
         <v>55</v>
@@ -2189,10 +2204,10 @@
         <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C20" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D20" t="s">
         <v>58</v>
@@ -2208,10 +2223,10 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C21" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D21" t="s">
         <v>61</v>
@@ -2227,10 +2242,10 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C22" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D22" t="s">
         <v>64</v>
@@ -2246,10 +2261,10 @@
         <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C23" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D23" t="s">
         <v>67</v>
@@ -2265,10 +2280,10 @@
         <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C24" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D24" t="s">
         <v>70</v>
@@ -2284,10 +2299,10 @@
         <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C25" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D25" t="s">
         <v>73</v>
@@ -2303,10 +2318,10 @@
         <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C26" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D26" t="s">
         <v>76</v>
@@ -2322,10 +2337,10 @@
         <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C27" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
@@ -2341,10 +2356,10 @@
         <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C28" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D28" t="s">
         <v>82</v>
@@ -2360,10 +2375,10 @@
         <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C29" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D29" t="s">
         <v>85</v>
@@ -2379,10 +2394,10 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C30" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D30" t="s">
         <v>88</v>
@@ -2398,10 +2413,10 @@
         <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C31" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D31" t="s">
         <v>91</v>
@@ -2417,10 +2432,10 @@
         <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C32" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D32" t="s">
         <v>94</v>
@@ -2436,10 +2451,10 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C33" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D33" t="s">
         <v>97</v>
@@ -2455,10 +2470,10 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C34" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D34" t="s">
         <v>100</v>
@@ -2474,10 +2489,10 @@
         <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C35" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D35" t="s">
         <v>103</v>
@@ -2493,10 +2508,10 @@
         <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C36" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D36" t="s">
         <v>106</v>
@@ -2512,10 +2527,10 @@
         <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C37" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -2531,10 +2546,10 @@
         <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C38" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D38" t="s">
         <v>112</v>
@@ -2550,10 +2565,10 @@
         <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C39" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D39" t="s">
         <v>115</v>
@@ -2569,10 +2584,10 @@
         <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C40" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D40" t="s">
         <v>118</v>
@@ -2588,10 +2603,10 @@
         <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C41" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D41" t="s">
         <v>121</v>
@@ -2607,10 +2622,10 @@
         <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C42" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D42" t="s">
         <v>124</v>
@@ -2626,10 +2641,10 @@
         <v>126</v>
       </c>
       <c r="B43" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C43" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D43" t="s">
         <v>127</v>
@@ -2645,10 +2660,10 @@
         <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C44" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D44" t="s">
         <v>130</v>
@@ -2664,10 +2679,10 @@
         <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C45" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D45" t="s">
         <v>133</v>
@@ -2683,10 +2698,10 @@
         <v>135</v>
       </c>
       <c r="B46" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C46" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D46" t="s">
         <v>82</v>
@@ -2702,10 +2717,10 @@
         <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C47" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D47" t="s">
         <v>138</v>
@@ -2721,10 +2736,10 @@
         <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C48" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="D48" t="s">
         <v>141</v>
@@ -2740,10 +2755,10 @@
         <v>143</v>
       </c>
       <c r="B49" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C49" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -2759,10 +2774,10 @@
         <v>144</v>
       </c>
       <c r="B50" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C50" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D50" t="s">
         <v>44</v>
@@ -2778,10 +2793,10 @@
         <v>146</v>
       </c>
       <c r="B51" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C51" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D51" t="s">
         <v>147</v>
@@ -2797,10 +2812,10 @@
         <v>149</v>
       </c>
       <c r="B52" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C52" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D52" t="s">
         <v>150</v>
@@ -2816,10 +2831,10 @@
         <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C53" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D53" t="s">
         <v>153</v>
@@ -2835,10 +2850,10 @@
         <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C54" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D54" t="s">
         <v>156</v>
@@ -2854,10 +2869,10 @@
         <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C55" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D55" t="s">
         <v>159</v>
@@ -2873,10 +2888,10 @@
         <v>161</v>
       </c>
       <c r="B56" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C56" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D56" t="s">
         <v>162</v>
@@ -2892,10 +2907,10 @@
         <v>164</v>
       </c>
       <c r="B57" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C57" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D57" t="s">
         <v>165</v>
@@ -2911,10 +2926,10 @@
         <v>167</v>
       </c>
       <c r="B58" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C58" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="D58" t="s">
         <v>168</v>
@@ -2930,10 +2945,10 @@
         <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C59" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D59" t="s">
         <v>171</v>
@@ -2949,10 +2964,10 @@
         <v>173</v>
       </c>
       <c r="B60" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C60" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D60" t="s">
         <v>174</v>
@@ -2968,10 +2983,10 @@
         <v>176</v>
       </c>
       <c r="B61" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C61" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D61" t="s">
         <v>177</v>
@@ -2987,10 +3002,10 @@
         <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C62" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D62" t="s">
         <v>180</v>
@@ -3006,10 +3021,10 @@
         <v>182</v>
       </c>
       <c r="B63" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C63" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D63" t="s">
         <v>183</v>
@@ -3025,10 +3040,10 @@
         <v>185</v>
       </c>
       <c r="B64" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C64" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D64" t="s">
         <v>186</v>
@@ -3044,10 +3059,10 @@
         <v>188</v>
       </c>
       <c r="B65" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C65" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D65" t="s">
         <v>189</v>
@@ -3063,10 +3078,10 @@
         <v>191</v>
       </c>
       <c r="B66" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C66" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D66" t="s">
         <v>192</v>
@@ -3082,10 +3097,10 @@
         <v>194</v>
       </c>
       <c r="B67" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C67" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D67" t="s">
         <v>195</v>
@@ -3101,10 +3116,10 @@
         <v>197</v>
       </c>
       <c r="B68" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C68" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D68" t="s">
         <v>198</v>
@@ -3120,10 +3135,10 @@
         <v>200</v>
       </c>
       <c r="B69" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C69" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="D69" t="s">
         <v>201</v>
@@ -3139,10 +3154,10 @@
         <v>203</v>
       </c>
       <c r="B70" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C70" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D70" t="s">
         <v>204</v>
@@ -3158,10 +3173,10 @@
         <v>206</v>
       </c>
       <c r="B71" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C71" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="D71" t="s">
         <v>207</v>
@@ -3177,10 +3192,10 @@
         <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C72" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="D72" t="s">
         <v>210</v>
@@ -3196,10 +3211,10 @@
         <v>212</v>
       </c>
       <c r="B73" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C73" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D73" t="s">
         <v>213</v>
@@ -3215,10 +3230,10 @@
         <v>215</v>
       </c>
       <c r="B74" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C74" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="D74" t="s">
         <v>216</v>
@@ -3234,10 +3249,10 @@
         <v>218</v>
       </c>
       <c r="B75" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C75" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D75" t="s">
         <v>219</v>
@@ -3253,10 +3268,10 @@
         <v>221</v>
       </c>
       <c r="B76" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C76" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D76" t="s">
         <v>222</v>
@@ -3272,10 +3287,10 @@
         <v>224</v>
       </c>
       <c r="B77" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C77" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D77" t="s">
         <v>225</v>
@@ -3291,10 +3306,10 @@
         <v>227</v>
       </c>
       <c r="B78" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C78" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D78" t="s">
         <v>228</v>
@@ -3310,10 +3325,10 @@
         <v>230</v>
       </c>
       <c r="B79" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C79" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D79" t="s">
         <v>231</v>
@@ -3329,10 +3344,10 @@
         <v>233</v>
       </c>
       <c r="B80" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C80" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="D80" t="s">
         <v>234</v>
@@ -3348,10 +3363,10 @@
         <v>236</v>
       </c>
       <c r="B81" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C81" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D81" t="s">
         <v>237</v>
@@ -3367,10 +3382,10 @@
         <v>239</v>
       </c>
       <c r="B82" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C82" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="D82" t="s">
         <v>240</v>
@@ -3386,10 +3401,10 @@
         <v>242</v>
       </c>
       <c r="B83" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C83" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D83" t="s">
         <v>243</v>
@@ -3405,10 +3420,10 @@
         <v>244</v>
       </c>
       <c r="B84" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C84" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="D84" t="s">
         <v>245</v>
@@ -3424,10 +3439,10 @@
         <v>247</v>
       </c>
       <c r="B85" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C85" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D85" t="s">
         <v>248</v>
@@ -3443,10 +3458,10 @@
         <v>250</v>
       </c>
       <c r="B86" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C86" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D86" t="s">
         <v>109</v>
@@ -3462,10 +3477,10 @@
         <v>251</v>
       </c>
       <c r="B87" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C87" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="D87" t="s">
         <v>252</v>
@@ -3481,10 +3496,10 @@
         <v>254</v>
       </c>
       <c r="B88" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C88" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D88" t="s">
         <v>109</v>
@@ -3500,10 +3515,10 @@
         <v>255</v>
       </c>
       <c r="B89" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C89" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D89" t="s">
         <v>109</v>
@@ -3519,10 +3534,10 @@
         <v>256</v>
       </c>
       <c r="B90" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C90" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D90" t="s">
         <v>109</v>
@@ -3538,10 +3553,10 @@
         <v>257</v>
       </c>
       <c r="B91" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C91" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="D91" t="s">
         <v>258</v>
@@ -3557,10 +3572,10 @@
         <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C92" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="D92" t="s">
         <v>261</v>
@@ -3576,10 +3591,10 @@
         <v>263</v>
       </c>
       <c r="B93" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C93" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="D93" t="s">
         <v>264</v>
@@ -3595,10 +3610,10 @@
         <v>266</v>
       </c>
       <c r="B94" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C94" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D94" t="s">
         <v>267</v>
@@ -3614,10 +3629,10 @@
         <v>269</v>
       </c>
       <c r="B95" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C95" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D95" t="s">
         <v>270</v>
@@ -3633,10 +3648,10 @@
         <v>272</v>
       </c>
       <c r="B96" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C96" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="D96" t="s">
         <v>273</v>
@@ -3652,10 +3667,10 @@
         <v>275</v>
       </c>
       <c r="B97" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C97" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="D97" t="s">
         <v>276</v>
@@ -3671,10 +3686,10 @@
         <v>278</v>
       </c>
       <c r="B98" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C98" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D98" t="s">
         <v>279</v>
@@ -3690,10 +3705,10 @@
         <v>281</v>
       </c>
       <c r="B99" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C99" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D99" t="s">
         <v>279</v>
@@ -3709,10 +3724,10 @@
         <v>282</v>
       </c>
       <c r="B100" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C100" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D100" t="s">
         <v>100</v>
@@ -3728,10 +3743,10 @@
         <v>283</v>
       </c>
       <c r="B101" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C101" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D101" t="s">
         <v>100</v>
@@ -3747,10 +3762,10 @@
         <v>284</v>
       </c>
       <c r="B102" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C102" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="D102" t="s">
         <v>285</v>
@@ -3766,10 +3781,10 @@
         <v>287</v>
       </c>
       <c r="B103" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C103" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D103" t="s">
         <v>288</v>
@@ -3785,10 +3800,10 @@
         <v>290</v>
       </c>
       <c r="B104" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C104" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="D104" t="s">
         <v>79</v>
@@ -3804,10 +3819,10 @@
         <v>291</v>
       </c>
       <c r="B105" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C105" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D105" t="s">
         <v>292</v>
@@ -3823,10 +3838,10 @@
         <v>294</v>
       </c>
       <c r="B106" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C106" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D106" t="s">
         <v>295</v>
@@ -3842,10 +3857,10 @@
         <v>297</v>
       </c>
       <c r="B107" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C107" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D107" t="s">
         <v>298</v>
@@ -3861,10 +3876,10 @@
         <v>300</v>
       </c>
       <c r="B108" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C108" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D108" t="s">
         <v>301</v>
@@ -3880,276 +3895,276 @@
         <v>303</v>
       </c>
       <c r="B109" t="s">
-        <v>434</v>
+        <v>9</v>
       </c>
       <c r="C109" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="D109" t="s">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="E109" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="G109"/>
       <c r="H109"/>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B110" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C110" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D110" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E110" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G110"/>
       <c r="H110"/>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B111" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C111" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D111" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E111" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G111"/>
       <c r="H111"/>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B112" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C112" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D112" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E112" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G112"/>
       <c r="H112"/>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B113" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C113" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D113" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E113" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G113"/>
       <c r="H113"/>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B114" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C114" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D114" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E114" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G114"/>
       <c r="H114"/>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B115" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C115" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D115" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E115" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G115"/>
       <c r="H115"/>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B116" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C116" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D116" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E116" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G116"/>
       <c r="H116"/>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B117" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C117" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D117" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E117" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G117"/>
       <c r="H117"/>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B118" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C118" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D118" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E118" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G118"/>
       <c r="H118"/>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B119" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C119" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D119" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E119" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G119"/>
       <c r="H119"/>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B120" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C120" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="D120" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E120" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G120"/>
       <c r="H120"/>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B121" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C121" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D121" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E121" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G121"/>
       <c r="H121"/>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B122" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C122" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D122" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E122" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G122"/>
       <c r="H122"/>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B123" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C123" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D123" t="s">
         <v>22</v>
@@ -4162,459 +4177,475 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B124" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C124" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D124" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E124" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G124"/>
       <c r="H124"/>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B125" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C125" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="D125" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E125" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G125"/>
       <c r="H125"/>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B126" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C126" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="D126" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E126" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G126"/>
       <c r="H126"/>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B127" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C127" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="D127" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E127" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G127"/>
       <c r="H127"/>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B128" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C128" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D128" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E128" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G128"/>
       <c r="H128"/>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B129" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C129" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D129" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E129" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G129"/>
       <c r="H129"/>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B130" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C130" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D130" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E130" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G130"/>
       <c r="H130"/>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B131" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C131" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D131" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E131" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G131"/>
       <c r="H131"/>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B132" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C132" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D132" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E132" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G132"/>
       <c r="H132"/>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B133" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C133" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D133" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E133" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G133"/>
       <c r="H133"/>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B134" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C134" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D134" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E134" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G134"/>
       <c r="H134"/>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B135" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C135" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E135" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G135"/>
       <c r="H135"/>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B136" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C136" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E136" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G136"/>
       <c r="H136"/>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B137" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C137" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E137" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G137"/>
       <c r="H137"/>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B138" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C138" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E138" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G138"/>
       <c r="H138"/>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B139" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C139" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D139" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E139" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G139"/>
       <c r="H139"/>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B140" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C140" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D140" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E140" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G140"/>
       <c r="H140"/>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B141" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C141" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="D141" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E141" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G141"/>
       <c r="H141"/>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B142" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C142" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D142" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E142" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G142"/>
       <c r="H142"/>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B143" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C143" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D143" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E143" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G143"/>
       <c r="H143"/>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B144" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C144" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G144"/>
       <c r="H144"/>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B145" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C145" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E145" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G145"/>
       <c r="H145"/>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B146" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C146" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D146" t="s">
         <v>159</v>
       </c>
       <c r="E146" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G146"/>
       <c r="H146"/>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B147" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C147" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D147" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E147" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G147"/>
       <c r="H147"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>417</v>
+      </c>
+      <c r="B148" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" t="s">
+        <v>418</v>
+      </c>
+      <c r="E148" t="s">
+        <v>419</v>
+      </c>
+      <c r="G148"/>
+      <c r="H148"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
